--- a/output/CodeSystem-presenting-complaints.xlsx
+++ b/output/CodeSystem-presenting-complaints.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Presenting Complaint codes</t>
+    <t>Local code system specifying Presenting Complaint codes</t>
   </si>
   <si>
     <t>Purpose</t>
